--- a/data/trans_camb/P57_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Clase-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 2,6</t>
+          <t>-6,93; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 1,17</t>
+          <t>-6,8; 1,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,21</t>
+          <t>-6,02; 0,19</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 26,12</t>
+          <t>-41,87; 23,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 16,62</t>
+          <t>-49,88; 15,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 2,31</t>
+          <t>-40,67; 2,96</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,34</t>
+          <t>-6,72; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 2,65</t>
+          <t>-7,3; 2,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,81</t>
+          <t>-5,59; 1,13</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 25,42</t>
+          <t>-44,41; 18,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 23,34</t>
+          <t>-39,2; 24,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 7,13</t>
+          <t>-36,05; 10,95</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,87; -6,22</t>
+          <t>-21,65; -5,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -2,37</t>
+          <t>-20,18; -3,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,15; -7,15</t>
+          <t>-22,61; -6,93</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,83; -28,26</t>
+          <t>-84,53; -27,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,14; -7,17</t>
+          <t>-55,35; -11,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,91; -29,71</t>
+          <t>-80,63; -28,8</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,62; -0,71</t>
+          <t>-7,15; -0,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,55; -7,2</t>
+          <t>-16,97; -7,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -4,82</t>
+          <t>-11,2; -5,07</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,75; -3,68</t>
+          <t>-35,65; -3,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,73; -37,32</t>
+          <t>-76,38; -37,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,12; -26,16</t>
+          <t>-55,65; -27,1</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -2,8</t>
+          <t>-12,75; -3,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -3,96</t>
+          <t>-16,88; -4,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -4,82</t>
+          <t>-12,57; -4,7</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,13; -10,01</t>
+          <t>-42,98; -12,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,9; -13,99</t>
+          <t>-47,68; -14,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,65; -16,88</t>
+          <t>-40,92; -16,93</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 2,22</t>
+          <t>-5,85; 2,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 0,35</t>
+          <t>-7,48; 0,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -0,57</t>
+          <t>-6,93; -0,63</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-74,51; 56,47</t>
+          <t>-71,23; 66,79</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 1,26</t>
+          <t>-26,27; 1,84</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-30,4; -2,97</t>
+          <t>-29,69; -3,06</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -3,8</t>
+          <t>-8,89; -4,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -5,46</t>
+          <t>-10,84; -5,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -5,22</t>
+          <t>-8,94; -5,17</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-46,62; -21,96</t>
+          <t>-48,86; -23,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -23,92</t>
+          <t>-44,6; -24,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,04; -25,53</t>
+          <t>-41,72; -25,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-2,16</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-2,17</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,64</t>
+          <t>-2,22</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 2,43</t>
+          <t>-6,55; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 1,28</t>
+          <t>-6,6; 1,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,19</t>
+          <t>-5,65; 0,59</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-16,85%</t>
+          <t>-15,89%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-25,94%</t>
+          <t>-19,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-21,02%</t>
+          <t>-17,66%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,87; 23,89</t>
+          <t>-40,0; 21,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 15,13</t>
+          <t>-46,8; 22,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 2,96</t>
+          <t>-38,43; 5,6</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-2,37</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 1,77</t>
+          <t>-7,13; 1,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,8</t>
+          <t>-6,64; 3,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 1,13</t>
+          <t>-5,48; 1,06</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-19,5%</t>
+          <t>-21,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-14,11%</t>
+          <t>-13,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-17,35%</t>
+          <t>-17,68%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,41; 18,82</t>
+          <t>-45,78; 13,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 24,52</t>
+          <t>-37,46; 25,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 10,95</t>
+          <t>-35,68; 9,3</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-12,87</t>
+          <t>-7,98</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-11,13</t>
+          <t>-11,82</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-12,84</t>
+          <t>-8,73</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,65; -5,73</t>
+          <t>-12,99; -3,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,18; -3,38</t>
+          <t>-21,09; -2,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,61; -6,93</t>
+          <t>-12,97; -4,26</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-57,54%</t>
+          <t>-35,67%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-36,85%</t>
+          <t>-39,13%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-52,95%</t>
+          <t>-35,99%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,53; -27,12</t>
+          <t>-52,03; -16,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,35; -11,11</t>
+          <t>-57,66; -11,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,63; -28,8</t>
+          <t>-48,21; -19,39</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-4,31</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-11,17</t>
+          <t>-8,32</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,34</t>
+          <t>-6,02</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -0,66</t>
+          <t>-7,4; -0,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -7,08</t>
+          <t>-11,62; -4,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -5,07</t>
+          <t>-8,2; -3,56</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-20,89%</t>
+          <t>-22,81%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-54,08%</t>
+          <t>-40,3%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-37,4%</t>
+          <t>-30,67%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,65; -3,88</t>
+          <t>-35,95; -5,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,38; -37,5</t>
+          <t>-51,14; -26,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,65; -27,1</t>
+          <t>-39,71; -19,86</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-7,77</t>
+          <t>-8,16</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-9,31</t>
+          <t>-6,18</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-8,34</t>
+          <t>-6,77</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,75; -3,04</t>
+          <t>-12,62; -3,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,88; -4,43</t>
+          <t>-10,41; -1,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -4,7</t>
+          <t>-10,02; -3,64</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-28,36%</t>
+          <t>-29,8%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-29,39%</t>
+          <t>-19,49%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-28,07%</t>
+          <t>-22,76%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,98; -12,08</t>
+          <t>-41,84; -11,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,68; -14,84</t>
+          <t>-29,9; -6,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,92; -16,93</t>
+          <t>-31,47; -13,11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-1,03</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,84</t>
+          <t>-3,61</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 2,47</t>
+          <t>-5,33; 3,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 0,45</t>
+          <t>-7,81; -0,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -0,63</t>
+          <t>-6,55; -0,5</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-29,83%</t>
+          <t>-16,44%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-13,97%</t>
+          <t>-15,64%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-17,52%</t>
+          <t>-16,48%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 66,79</t>
+          <t>-63,08; 98,17</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 1,84</t>
+          <t>-27,75; -1,77</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,69; -3,06</t>
+          <t>-27,99; -2,26</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-5,96</t>
+          <t>-5,03</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-7,62</t>
+          <t>-6,02</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-6,8</t>
+          <t>-5,52</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -4,01</t>
+          <t>-6,89; -2,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,84; -5,52</t>
+          <t>-7,85; -4,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -5,17</t>
+          <t>-6,76; -4,2</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-32,22%</t>
+          <t>-27,16%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-32,42%</t>
+          <t>-25,59%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-32,28%</t>
+          <t>-26,22%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-48,86; -23,28</t>
+          <t>-34,9; -17,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-44,6; -24,35</t>
+          <t>-31,75; -19,07</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,72; -25,35</t>
+          <t>-30,92; -20,63</t>
         </is>
       </c>
     </row>
